--- a/HACKER3_Test6_Final_Architecture.xlsx
+++ b/HACKER3_Test6_Final_Architecture.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Testweb\testweb\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Test_Info" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Test_Data" sheetId="2" r:id="rId5"/>
+    <sheet name="Test_Info" sheetId="1" r:id="rId1"/>
+    <sheet name="Test_Data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="YuZ6jze6cbBiaRUP/HZno6fH8PbBBY0WWX3VbcnNl24="/>
@@ -17,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="1531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="1532">
   <si>
     <t>test_id</t>
   </si>
@@ -4610,33 +4618,36 @@
   </si>
   <si>
     <t>Giải thích: (A) Nhân viên sẽ gặp nhau ở đâu vào sáng ngày 29 tháng 8: Memo ghi: 'Our first event for the day will be a softball match, so we will meet first thing at the venue's softball field at 10 A.M.' (...CHÚNG TA SẼ GẶP NHAU VÀO ĐẦU GIỜ TẠI SÂN BÓNG MỀM...). Tra trong bảng Facility, Softball field nằm ở Zone 1. Vậy họ sẽ gặp nhau ở Zone 1.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14yGl8HQLGWVQRJ9wKb3tllrgH0prTzdC/view?usp=drive_link</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
     </font>
@@ -4646,7 +4657,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -4662,7 +4673,13 @@
     </fill>
   </fills>
   <borders count="4">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -4676,6 +4693,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4690,6 +4708,7 @@
       <bottom style="thin">
         <color rgb="FFCBD5E1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4704,60 +4723,58 @@
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -4947,24 +4964,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="25.0"/>
-    <col customWidth="1" min="3" max="3" width="60.0"/>
-    <col customWidth="1" min="4" max="5" width="20.0"/>
-    <col customWidth="1" min="6" max="26" width="8.71"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="6" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4981,1028 +4998,1026 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="3" t="s">
+        <v>1531</v>
+      </c>
       <c r="D2" s="4">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="E2" s="4">
-        <v>200.0</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z797"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="6.0"/>
-    <col customWidth="1" min="3" max="3" width="12.0"/>
-    <col customWidth="1" min="4" max="5" width="25.0"/>
-    <col customWidth="1" min="6" max="6" width="71.14"/>
-    <col customWidth="1" min="7" max="7" width="102.14"/>
-    <col customWidth="1" min="8" max="11" width="25.0"/>
-    <col customWidth="1" min="12" max="12" width="12.0"/>
-    <col customWidth="1" min="13" max="13" width="60.0"/>
-    <col customWidth="1" min="14" max="26" width="8.71"/>
+    <col min="1" max="2" width="6" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="71.140625" customWidth="1"/>
+    <col min="7" max="7" width="102.140625" customWidth="1"/>
+    <col min="8" max="11" width="25" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="60" customWidth="1"/>
+    <col min="14" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
@@ -6043,7 +6058,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
@@ -6089,7 +6104,7 @@
       <c r="Y2" s="8"/>
       <c r="Z2" s="8"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
@@ -6135,7 +6150,7 @@
       <c r="Y3" s="8"/>
       <c r="Z3" s="8"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>36</v>
       </c>
@@ -6181,7 +6196,7 @@
       <c r="Y4" s="8"/>
       <c r="Z4" s="8"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>44</v>
       </c>
@@ -6227,7 +6242,7 @@
       <c r="Y5" s="8"/>
       <c r="Z5" s="8"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>52</v>
       </c>
@@ -6273,7 +6288,7 @@
       <c r="Y6" s="8"/>
       <c r="Z6" s="8"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>59</v>
       </c>
@@ -6319,7 +6334,7 @@
       <c r="Y7" s="8"/>
       <c r="Z7" s="8"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>66</v>
       </c>
@@ -6365,7 +6380,7 @@
       <c r="Y8" s="8"/>
       <c r="Z8" s="8"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>73</v>
       </c>
@@ -6411,7 +6426,7 @@
       <c r="Y9" s="8"/>
       <c r="Z9" s="8"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>80</v>
       </c>
@@ -6457,7 +6472,7 @@
       <c r="Y10" s="8"/>
       <c r="Z10" s="8"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>87</v>
       </c>
@@ -6503,7 +6518,7 @@
       <c r="Y11" s="8"/>
       <c r="Z11" s="8"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>94</v>
       </c>
@@ -6549,7 +6564,7 @@
       <c r="Y12" s="8"/>
       <c r="Z12" s="8"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>101</v>
       </c>
@@ -6595,7 +6610,7 @@
       <c r="Y13" s="8"/>
       <c r="Z13" s="8"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>108</v>
       </c>
@@ -6641,7 +6656,7 @@
       <c r="Y14" s="8"/>
       <c r="Z14" s="8"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>115</v>
       </c>
@@ -6687,7 +6702,7 @@
       <c r="Y15" s="8"/>
       <c r="Z15" s="8"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>122</v>
       </c>
@@ -6733,7 +6748,7 @@
       <c r="Y16" s="8"/>
       <c r="Z16" s="8"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>129</v>
       </c>
@@ -6779,7 +6794,7 @@
       <c r="Y17" s="8"/>
       <c r="Z17" s="8"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>136</v>
       </c>
@@ -6825,7 +6840,7 @@
       <c r="Y18" s="8"/>
       <c r="Z18" s="8"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>143</v>
       </c>
@@ -6871,7 +6886,7 @@
       <c r="Y19" s="8"/>
       <c r="Z19" s="8"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>150</v>
       </c>
@@ -6917,7 +6932,7 @@
       <c r="Y20" s="8"/>
       <c r="Z20" s="8"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>157</v>
       </c>
@@ -6963,7 +6978,7 @@
       <c r="Y21" s="8"/>
       <c r="Z21" s="8"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>164</v>
       </c>
@@ -7009,7 +7024,7 @@
       <c r="Y22" s="8"/>
       <c r="Z22" s="8"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>171</v>
       </c>
@@ -7055,7 +7070,7 @@
       <c r="Y23" s="8"/>
       <c r="Z23" s="8"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>178</v>
       </c>
@@ -7101,7 +7116,7 @@
       <c r="Y24" s="8"/>
       <c r="Z24" s="8"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>185</v>
       </c>
@@ -7147,7 +7162,7 @@
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>192</v>
       </c>
@@ -7193,7 +7208,7 @@
       <c r="Y26" s="8"/>
       <c r="Z26" s="8"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>199</v>
       </c>
@@ -7239,7 +7254,7 @@
       <c r="Y27" s="8"/>
       <c r="Z27" s="8"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>206</v>
       </c>
@@ -7285,7 +7300,7 @@
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>213</v>
       </c>
@@ -7331,7 +7346,7 @@
       <c r="Y29" s="8"/>
       <c r="Z29" s="8"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>220</v>
       </c>
@@ -7377,7 +7392,7 @@
       <c r="Y30" s="8"/>
       <c r="Z30" s="8"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>227</v>
       </c>
@@ -7423,7 +7438,7 @@
       <c r="Y31" s="8"/>
       <c r="Z31" s="8"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>234</v>
       </c>
@@ -7469,7 +7484,7 @@
       <c r="Y32" s="8"/>
       <c r="Z32" s="8"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>241</v>
       </c>
@@ -7519,7 +7534,7 @@
       <c r="Y33" s="8"/>
       <c r="Z33" s="8"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>250</v>
       </c>
@@ -7569,7 +7584,7 @@
       <c r="Y34" s="8"/>
       <c r="Z34" s="8"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>257</v>
       </c>
@@ -7619,7 +7634,7 @@
       <c r="Y35" s="8"/>
       <c r="Z35" s="8"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>264</v>
       </c>
@@ -7669,7 +7684,7 @@
       <c r="Y36" s="8"/>
       <c r="Z36" s="8"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>273</v>
       </c>
@@ -7719,7 +7734,7 @@
       <c r="Y37" s="8"/>
       <c r="Z37" s="8"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>280</v>
       </c>
@@ -7769,7 +7784,7 @@
       <c r="Y38" s="8"/>
       <c r="Z38" s="8"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>287</v>
       </c>
@@ -7819,7 +7834,7 @@
       <c r="Y39" s="8"/>
       <c r="Z39" s="8"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>296</v>
       </c>
@@ -7869,7 +7884,7 @@
       <c r="Y40" s="8"/>
       <c r="Z40" s="8"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>303</v>
       </c>
@@ -7919,7 +7934,7 @@
       <c r="Y41" s="8"/>
       <c r="Z41" s="8"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>310</v>
       </c>
@@ -7969,7 +7984,7 @@
       <c r="Y42" s="8"/>
       <c r="Z42" s="8"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>319</v>
       </c>
@@ -8019,7 +8034,7 @@
       <c r="Y43" s="8"/>
       <c r="Z43" s="8"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>326</v>
       </c>
@@ -8069,7 +8084,7 @@
       <c r="Y44" s="8"/>
       <c r="Z44" s="8"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>333</v>
       </c>
@@ -8119,7 +8134,7 @@
       <c r="Y45" s="8"/>
       <c r="Z45" s="8"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>342</v>
       </c>
@@ -8169,7 +8184,7 @@
       <c r="Y46" s="8"/>
       <c r="Z46" s="8"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>349</v>
       </c>
@@ -8219,7 +8234,7 @@
       <c r="Y47" s="8"/>
       <c r="Z47" s="8"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>356</v>
       </c>
@@ -8269,7 +8284,7 @@
       <c r="Y48" s="8"/>
       <c r="Z48" s="8"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>365</v>
       </c>
@@ -8319,7 +8334,7 @@
       <c r="Y49" s="8"/>
       <c r="Z49" s="8"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>372</v>
       </c>
@@ -8369,7 +8384,7 @@
       <c r="Y50" s="8"/>
       <c r="Z50" s="8"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>379</v>
       </c>
@@ -8419,7 +8434,7 @@
       <c r="Y51" s="8"/>
       <c r="Z51" s="8"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>388</v>
       </c>
@@ -8469,7 +8484,7 @@
       <c r="Y52" s="8"/>
       <c r="Z52" s="8"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>395</v>
       </c>
@@ -8519,7 +8534,7 @@
       <c r="Y53" s="8"/>
       <c r="Z53" s="8"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>402</v>
       </c>
@@ -8569,7 +8584,7 @@
       <c r="Y54" s="8"/>
       <c r="Z54" s="8"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>411</v>
       </c>
@@ -8619,7 +8634,7 @@
       <c r="Y55" s="8"/>
       <c r="Z55" s="8"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>418</v>
       </c>
@@ -8669,7 +8684,7 @@
       <c r="Y56" s="8"/>
       <c r="Z56" s="8"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>425</v>
       </c>
@@ -8719,7 +8734,7 @@
       <c r="Y57" s="8"/>
       <c r="Z57" s="8"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>434</v>
       </c>
@@ -8769,7 +8784,7 @@
       <c r="Y58" s="8"/>
       <c r="Z58" s="8"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>441</v>
       </c>
@@ -8819,7 +8834,7 @@
       <c r="Y59" s="8"/>
       <c r="Z59" s="8"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>448</v>
       </c>
@@ -8869,7 +8884,7 @@
       <c r="Y60" s="8"/>
       <c r="Z60" s="8"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>457</v>
       </c>
@@ -8919,7 +8934,7 @@
       <c r="Y61" s="8"/>
       <c r="Z61" s="8"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>464</v>
       </c>
@@ -8969,7 +8984,7 @@
       <c r="Y62" s="8"/>
       <c r="Z62" s="8"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>471</v>
       </c>
@@ -9019,7 +9034,7 @@
       <c r="Y63" s="8"/>
       <c r="Z63" s="8"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>480</v>
       </c>
@@ -9069,7 +9084,7 @@
       <c r="Y64" s="8"/>
       <c r="Z64" s="8"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>487</v>
       </c>
@@ -9119,7 +9134,7 @@
       <c r="Y65" s="8"/>
       <c r="Z65" s="8"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>494</v>
       </c>
@@ -9169,7 +9184,7 @@
       <c r="Y66" s="8"/>
       <c r="Z66" s="8"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>503</v>
       </c>
@@ -9219,7 +9234,7 @@
       <c r="Y67" s="8"/>
       <c r="Z67" s="8"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>510</v>
       </c>
@@ -9269,7 +9284,7 @@
       <c r="Y68" s="8"/>
       <c r="Z68" s="8"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>516</v>
       </c>
@@ -9319,7 +9334,7 @@
       <c r="Y69" s="8"/>
       <c r="Z69" s="8"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>525</v>
       </c>
@@ -9369,7 +9384,7 @@
       <c r="Y70" s="8"/>
       <c r="Z70" s="8"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>532</v>
       </c>
@@ -9419,7 +9434,7 @@
       <c r="Y71" s="8"/>
       <c r="Z71" s="8"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>539</v>
       </c>
@@ -9469,7 +9484,7 @@
       <c r="Y72" s="8"/>
       <c r="Z72" s="8"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>548</v>
       </c>
@@ -9519,7 +9534,7 @@
       <c r="Y73" s="8"/>
       <c r="Z73" s="8"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>555</v>
       </c>
@@ -9569,7 +9584,7 @@
       <c r="Y74" s="8"/>
       <c r="Z74" s="8"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>562</v>
       </c>
@@ -9619,7 +9634,7 @@
       <c r="Y75" s="8"/>
       <c r="Z75" s="8"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>571</v>
       </c>
@@ -9669,7 +9684,7 @@
       <c r="Y76" s="8"/>
       <c r="Z76" s="8"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>578</v>
       </c>
@@ -9719,7 +9734,7 @@
       <c r="Y77" s="8"/>
       <c r="Z77" s="8"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>585</v>
       </c>
@@ -9769,7 +9784,7 @@
       <c r="Y78" s="8"/>
       <c r="Z78" s="8"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
         <v>594</v>
       </c>
@@ -9819,7 +9834,7 @@
       <c r="Y79" s="8"/>
       <c r="Z79" s="8"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>601</v>
       </c>
@@ -9869,7 +9884,7 @@
       <c r="Y80" s="8"/>
       <c r="Z80" s="8"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
         <v>608</v>
       </c>
@@ -9919,7 +9934,7 @@
       <c r="Y81" s="8"/>
       <c r="Z81" s="8"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>617</v>
       </c>
@@ -9969,7 +9984,7 @@
       <c r="Y82" s="8"/>
       <c r="Z82" s="8"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>624</v>
       </c>
@@ -10019,7 +10034,7 @@
       <c r="Y83" s="8"/>
       <c r="Z83" s="8"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>631</v>
       </c>
@@ -10069,7 +10084,7 @@
       <c r="Y84" s="8"/>
       <c r="Z84" s="8"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>640</v>
       </c>
@@ -10119,7 +10134,7 @@
       <c r="Y85" s="8"/>
       <c r="Z85" s="8"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>647</v>
       </c>
@@ -10169,7 +10184,7 @@
       <c r="Y86" s="8"/>
       <c r="Z86" s="8"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>654</v>
       </c>
@@ -10219,7 +10234,7 @@
       <c r="Y87" s="8"/>
       <c r="Z87" s="8"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>663</v>
       </c>
@@ -10269,7 +10284,7 @@
       <c r="Y88" s="8"/>
       <c r="Z88" s="8"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>670</v>
       </c>
@@ -10319,7 +10334,7 @@
       <c r="Y89" s="8"/>
       <c r="Z89" s="8"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>677</v>
       </c>
@@ -10369,7 +10384,7 @@
       <c r="Y90" s="8"/>
       <c r="Z90" s="8"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>686</v>
       </c>
@@ -10419,7 +10434,7 @@
       <c r="Y91" s="8"/>
       <c r="Z91" s="8"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>693</v>
       </c>
@@ -10469,7 +10484,7 @@
       <c r="Y92" s="8"/>
       <c r="Z92" s="8"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>700</v>
       </c>
@@ -10519,7 +10534,7 @@
       <c r="Y93" s="8"/>
       <c r="Z93" s="8"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>709</v>
       </c>
@@ -10569,7 +10584,7 @@
       <c r="Y94" s="8"/>
       <c r="Z94" s="8"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
         <v>716</v>
       </c>
@@ -10619,7 +10634,7 @@
       <c r="Y95" s="8"/>
       <c r="Z95" s="8"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>723</v>
       </c>
@@ -10669,7 +10684,7 @@
       <c r="Y96" s="8"/>
       <c r="Z96" s="8"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
         <v>732</v>
       </c>
@@ -10719,7 +10734,7 @@
       <c r="Y97" s="8"/>
       <c r="Z97" s="8"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
         <v>739</v>
       </c>
@@ -10769,7 +10784,7 @@
       <c r="Y98" s="8"/>
       <c r="Z98" s="8"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
         <v>746</v>
       </c>
@@ -10819,7 +10834,7 @@
       <c r="Y99" s="8"/>
       <c r="Z99" s="8"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>755</v>
       </c>
@@ -10869,7 +10884,7 @@
       <c r="Y100" s="8"/>
       <c r="Z100" s="8"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>762</v>
       </c>
@@ -10919,7 +10934,7 @@
       <c r="Y101" s="8"/>
       <c r="Z101" s="8"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
         <v>769</v>
       </c>
@@ -10967,7 +10982,7 @@
       <c r="Y102" s="8"/>
       <c r="Z102" s="8"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
         <v>777</v>
       </c>
@@ -11015,7 +11030,7 @@
       <c r="Y103" s="8"/>
       <c r="Z103" s="8"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>785</v>
       </c>
@@ -11063,7 +11078,7 @@
       <c r="Y104" s="8"/>
       <c r="Z104" s="8"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>793</v>
       </c>
@@ -11111,7 +11126,7 @@
       <c r="Y105" s="8"/>
       <c r="Z105" s="8"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>801</v>
       </c>
@@ -11159,7 +11174,7 @@
       <c r="Y106" s="8"/>
       <c r="Z106" s="8"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>809</v>
       </c>
@@ -11207,7 +11222,7 @@
       <c r="Y107" s="8"/>
       <c r="Z107" s="8"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>817</v>
       </c>
@@ -11255,7 +11270,7 @@
       <c r="Y108" s="8"/>
       <c r="Z108" s="8"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
         <v>825</v>
       </c>
@@ -11303,7 +11318,7 @@
       <c r="Y109" s="8"/>
       <c r="Z109" s="8"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>833</v>
       </c>
@@ -11351,7 +11366,7 @@
       <c r="Y110" s="8"/>
       <c r="Z110" s="8"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>841</v>
       </c>
@@ -11399,7 +11414,7 @@
       <c r="Y111" s="8"/>
       <c r="Z111" s="8"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>849</v>
       </c>
@@ -11447,7 +11462,7 @@
       <c r="Y112" s="8"/>
       <c r="Z112" s="8"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
         <v>857</v>
       </c>
@@ -11495,7 +11510,7 @@
       <c r="Y113" s="8"/>
       <c r="Z113" s="8"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>865</v>
       </c>
@@ -11543,7 +11558,7 @@
       <c r="Y114" s="8"/>
       <c r="Z114" s="8"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
         <v>873</v>
       </c>
@@ -11591,7 +11606,7 @@
       <c r="Y115" s="8"/>
       <c r="Z115" s="8"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>881</v>
       </c>
@@ -11639,7 +11654,7 @@
       <c r="Y116" s="8"/>
       <c r="Z116" s="8"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
         <v>889</v>
       </c>
@@ -11687,7 +11702,7 @@
       <c r="Y117" s="8"/>
       <c r="Z117" s="8"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
         <v>897</v>
       </c>
@@ -11735,7 +11750,7 @@
       <c r="Y118" s="8"/>
       <c r="Z118" s="8"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
         <v>905</v>
       </c>
@@ -11783,7 +11798,7 @@
       <c r="Y119" s="8"/>
       <c r="Z119" s="8"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
         <v>913</v>
       </c>
@@ -11831,7 +11846,7 @@
       <c r="Y120" s="8"/>
       <c r="Z120" s="8"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
         <v>921</v>
       </c>
@@ -11879,7 +11894,7 @@
       <c r="Y121" s="8"/>
       <c r="Z121" s="8"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>929</v>
       </c>
@@ -11927,7 +11942,7 @@
       <c r="Y122" s="8"/>
       <c r="Z122" s="8"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
         <v>937</v>
       </c>
@@ -11975,7 +11990,7 @@
       <c r="Y123" s="8"/>
       <c r="Z123" s="8"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
         <v>945</v>
       </c>
@@ -12023,7 +12038,7 @@
       <c r="Y124" s="8"/>
       <c r="Z124" s="8"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
         <v>953</v>
       </c>
@@ -12071,7 +12086,7 @@
       <c r="Y125" s="8"/>
       <c r="Z125" s="8"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>961</v>
       </c>
@@ -12119,7 +12134,7 @@
       <c r="Y126" s="8"/>
       <c r="Z126" s="8"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
         <v>969</v>
       </c>
@@ -12167,7 +12182,7 @@
       <c r="Y127" s="8"/>
       <c r="Z127" s="8"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
         <v>977</v>
       </c>
@@ -12215,7 +12230,7 @@
       <c r="Y128" s="8"/>
       <c r="Z128" s="8"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
         <v>985</v>
       </c>
@@ -12263,7 +12278,7 @@
       <c r="Y129" s="8"/>
       <c r="Z129" s="8"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
         <v>993</v>
       </c>
@@ -12311,7 +12326,7 @@
       <c r="Y130" s="8"/>
       <c r="Z130" s="8"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
         <v>1001</v>
       </c>
@@ -12359,7 +12374,7 @@
       <c r="Y131" s="8"/>
       <c r="Z131" s="8"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
         <v>1009</v>
       </c>
@@ -12409,7 +12424,7 @@
       <c r="Y132" s="8"/>
       <c r="Z132" s="8"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
         <v>1018</v>
       </c>
@@ -12459,7 +12474,7 @@
       <c r="Y133" s="8"/>
       <c r="Z133" s="8"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
         <v>1025</v>
       </c>
@@ -12509,7 +12524,7 @@
       <c r="Y134" s="8"/>
       <c r="Z134" s="8"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
         <v>1032</v>
       </c>
@@ -12559,7 +12574,7 @@
       <c r="Y135" s="8"/>
       <c r="Z135" s="8"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>1039</v>
       </c>
@@ -12609,7 +12624,7 @@
       <c r="Y136" s="8"/>
       <c r="Z136" s="8"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
         <v>1048</v>
       </c>
@@ -12659,7 +12674,7 @@
       <c r="Y137" s="8"/>
       <c r="Z137" s="8"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
         <v>1055</v>
       </c>
@@ -12709,7 +12724,7 @@
       <c r="Y138" s="8"/>
       <c r="Z138" s="8"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
         <v>1062</v>
       </c>
@@ -12759,7 +12774,7 @@
       <c r="Y139" s="8"/>
       <c r="Z139" s="8"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
         <v>1069</v>
       </c>
@@ -12809,7 +12824,7 @@
       <c r="Y140" s="8"/>
       <c r="Z140" s="8"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>1078</v>
       </c>
@@ -12859,7 +12874,7 @@
       <c r="Y141" s="8"/>
       <c r="Z141" s="8"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
         <v>1085</v>
       </c>
@@ -12909,7 +12924,7 @@
       <c r="Y142" s="8"/>
       <c r="Z142" s="8"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
         <v>1092</v>
       </c>
@@ -12959,7 +12974,7 @@
       <c r="Y143" s="8"/>
       <c r="Z143" s="8"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
         <v>1099</v>
       </c>
@@ -13009,7 +13024,7 @@
       <c r="Y144" s="8"/>
       <c r="Z144" s="8"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
         <v>1108</v>
       </c>
@@ -13059,7 +13074,7 @@
       <c r="Y145" s="8"/>
       <c r="Z145" s="8"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>1115</v>
       </c>
@@ -13109,7 +13124,7 @@
       <c r="Y146" s="8"/>
       <c r="Z146" s="8"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
         <v>1122</v>
       </c>
@@ -13159,7 +13174,7 @@
       <c r="Y147" s="8"/>
       <c r="Z147" s="8"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>1129</v>
       </c>
@@ -13209,7 +13224,7 @@
       <c r="Y148" s="8"/>
       <c r="Z148" s="8"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
         <v>1138</v>
       </c>
@@ -13259,7 +13274,7 @@
       <c r="Y149" s="8"/>
       <c r="Z149" s="8"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>1145</v>
       </c>
@@ -13309,7 +13324,7 @@
       <c r="Y150" s="8"/>
       <c r="Z150" s="8"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>1154</v>
       </c>
@@ -13359,7 +13374,7 @@
       <c r="Y151" s="8"/>
       <c r="Z151" s="8"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>1161</v>
       </c>
@@ -13409,7 +13424,7 @@
       <c r="Y152" s="8"/>
       <c r="Z152" s="8"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
         <v>1170</v>
       </c>
@@ -13459,7 +13474,7 @@
       <c r="Y153" s="8"/>
       <c r="Z153" s="8"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
         <v>1177</v>
       </c>
@@ -13509,7 +13524,7 @@
       <c r="Y154" s="8"/>
       <c r="Z154" s="8"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
         <v>1186</v>
       </c>
@@ -13559,7 +13574,7 @@
       <c r="Y155" s="8"/>
       <c r="Z155" s="8"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>1193</v>
       </c>
@@ -13607,7 +13622,7 @@
       <c r="Y156" s="8"/>
       <c r="Z156" s="8"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>1201</v>
       </c>
@@ -13655,7 +13670,7 @@
       <c r="Y157" s="8"/>
       <c r="Z157" s="8"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>1208</v>
       </c>
@@ -13703,7 +13718,7 @@
       <c r="Y158" s="8"/>
       <c r="Z158" s="8"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
         <v>1215</v>
       </c>
@@ -13753,7 +13768,7 @@
       <c r="Y159" s="8"/>
       <c r="Z159" s="8"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
         <v>1224</v>
       </c>
@@ -13803,7 +13818,7 @@
       <c r="Y160" s="8"/>
       <c r="Z160" s="8"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
         <v>1231</v>
       </c>
@@ -13853,7 +13868,7 @@
       <c r="Y161" s="8"/>
       <c r="Z161" s="8"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
         <v>1238</v>
       </c>
@@ -13903,7 +13918,7 @@
       <c r="Y162" s="8"/>
       <c r="Z162" s="8"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
         <v>1247</v>
       </c>
@@ -13953,7 +13968,7 @@
       <c r="Y163" s="8"/>
       <c r="Z163" s="8"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
         <v>1254</v>
       </c>
@@ -14003,7 +14018,7 @@
       <c r="Y164" s="8"/>
       <c r="Z164" s="8"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
         <v>1261</v>
       </c>
@@ -14053,7 +14068,7 @@
       <c r="Y165" s="8"/>
       <c r="Z165" s="8"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>1270</v>
       </c>
@@ -14103,7 +14118,7 @@
       <c r="Y166" s="8"/>
       <c r="Z166" s="8"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
         <v>1277</v>
       </c>
@@ -14153,7 +14168,7 @@
       <c r="Y167" s="8"/>
       <c r="Z167" s="8"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
         <v>1284</v>
       </c>
@@ -14203,7 +14218,7 @@
       <c r="Y168" s="8"/>
       <c r="Z168" s="8"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
         <v>1291</v>
       </c>
@@ -14253,7 +14268,7 @@
       <c r="Y169" s="8"/>
       <c r="Z169" s="8"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
         <v>1300</v>
       </c>
@@ -14303,7 +14318,7 @@
       <c r="Y170" s="8"/>
       <c r="Z170" s="8"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
         <v>1307</v>
       </c>
@@ -14353,7 +14368,7 @@
       <c r="Y171" s="8"/>
       <c r="Z171" s="8"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
         <v>1314</v>
       </c>
@@ -14403,7 +14418,7 @@
       <c r="Y172" s="8"/>
       <c r="Z172" s="8"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
         <v>1317</v>
       </c>
@@ -14453,7 +14468,7 @@
       <c r="Y173" s="8"/>
       <c r="Z173" s="8"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
         <v>1326</v>
       </c>
@@ -14503,7 +14518,7 @@
       <c r="Y174" s="8"/>
       <c r="Z174" s="8"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
         <v>1333</v>
       </c>
@@ -14553,7 +14568,7 @@
       <c r="Y175" s="8"/>
       <c r="Z175" s="8"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>1340</v>
       </c>
@@ -14603,7 +14618,7 @@
       <c r="Y176" s="8"/>
       <c r="Z176" s="8"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
         <v>1347</v>
       </c>
@@ -14653,7 +14668,7 @@
       <c r="Y177" s="8"/>
       <c r="Z177" s="8"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
         <v>1356</v>
       </c>
@@ -14703,7 +14718,7 @@
       <c r="Y178" s="8"/>
       <c r="Z178" s="8"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
         <v>1363</v>
       </c>
@@ -14753,7 +14768,7 @@
       <c r="Y179" s="8"/>
       <c r="Z179" s="8"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
         <v>1370</v>
       </c>
@@ -14803,7 +14818,7 @@
       <c r="Y180" s="8"/>
       <c r="Z180" s="8"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
         <v>1377</v>
       </c>
@@ -14853,7 +14868,7 @@
       <c r="Y181" s="8"/>
       <c r="Z181" s="8"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
         <v>1384</v>
       </c>
@@ -14903,7 +14918,7 @@
       <c r="Y182" s="8"/>
       <c r="Z182" s="8"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
         <v>1393</v>
       </c>
@@ -14953,7 +14968,7 @@
       <c r="Y183" s="8"/>
       <c r="Z183" s="8"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
         <v>1400</v>
       </c>
@@ -15003,7 +15018,7 @@
       <c r="Y184" s="8"/>
       <c r="Z184" s="8"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
         <v>1407</v>
       </c>
@@ -15053,7 +15068,7 @@
       <c r="Y185" s="8"/>
       <c r="Z185" s="8"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>1414</v>
       </c>
@@ -15103,7 +15118,7 @@
       <c r="Y186" s="8"/>
       <c r="Z186" s="8"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
         <v>1421</v>
       </c>
@@ -15153,7 +15168,7 @@
       <c r="Y187" s="8"/>
       <c r="Z187" s="8"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
         <v>1430</v>
       </c>
@@ -15203,7 +15218,7 @@
       <c r="Y188" s="8"/>
       <c r="Z188" s="8"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
         <v>1436</v>
       </c>
@@ -15253,7 +15268,7 @@
       <c r="Y189" s="8"/>
       <c r="Z189" s="8"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
         <v>1443</v>
       </c>
@@ -15303,7 +15318,7 @@
       <c r="Y190" s="8"/>
       <c r="Z190" s="8"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
         <v>1450</v>
       </c>
@@ -15353,7 +15368,7 @@
       <c r="Y191" s="8"/>
       <c r="Z191" s="8"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
         <v>1457</v>
       </c>
@@ -15403,7 +15418,7 @@
       <c r="Y192" s="8"/>
       <c r="Z192" s="8"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
         <v>1466</v>
       </c>
@@ -15453,7 +15468,7 @@
       <c r="Y193" s="8"/>
       <c r="Z193" s="8"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
         <v>1473</v>
       </c>
@@ -15503,7 +15518,7 @@
       <c r="Y194" s="8"/>
       <c r="Z194" s="8"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
         <v>1480</v>
       </c>
@@ -15553,7 +15568,7 @@
       <c r="Y195" s="8"/>
       <c r="Z195" s="8"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>1487</v>
       </c>
@@ -15603,7 +15618,7 @@
       <c r="Y196" s="8"/>
       <c r="Z196" s="8"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
         <v>1494</v>
       </c>
@@ -15653,7 +15668,7 @@
       <c r="Y197" s="8"/>
       <c r="Z197" s="8"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
         <v>1503</v>
       </c>
@@ -15703,7 +15718,7 @@
       <c r="Y198" s="8"/>
       <c r="Z198" s="8"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
         <v>1510</v>
       </c>
@@ -15753,7 +15768,7 @@
       <c r="Y199" s="8"/>
       <c r="Z199" s="8"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
         <v>1517</v>
       </c>
@@ -15803,7 +15818,7 @@
       <c r="Y200" s="8"/>
       <c r="Z200" s="8"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
         <v>1524</v>
       </c>
@@ -15853,606 +15868,604 @@
       <c r="Y201" s="8"/>
       <c r="Z201" s="8"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>